--- a/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
+++ b/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
@@ -984,7 +984,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45184.56808889021</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1057,8 +1057,6 @@
       </c>
       <c r="E11" s="20" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
@@ -1066,12 +1064,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
@@ -1079,14 +1071,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30" ht="18" customHeight="1" s="17">
       <c r="A30" s="12" t="inlineStr">
         <is>
@@ -1119,7 +1103,7 @@
       </c>
       <c r="C31" s="19" t="n"/>
       <c r="D31" s="8" t="n">
-        <v>3963</v>
+        <v>4359.3</v>
       </c>
       <c r="E31" s="3" t="n"/>
     </row>
@@ -1136,7 +1120,7 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="10" t="n">
-        <v>3535</v>
+        <v>3888.5</v>
       </c>
       <c r="E32" s="3" t="n"/>
     </row>
@@ -1153,7 +1137,7 @@
       </c>
       <c r="C33" s="19" t="n"/>
       <c r="D33" s="8" t="n">
-        <v>3371</v>
+        <v>3708.1</v>
       </c>
       <c r="E33" s="3" t="n"/>
     </row>
@@ -1170,7 +1154,7 @@
       </c>
       <c r="C34" s="19" t="n"/>
       <c r="D34" s="10" t="n">
-        <v>5741</v>
+        <v>6315.1</v>
       </c>
       <c r="E34" s="3" t="n"/>
     </row>
@@ -1187,7 +1171,7 @@
       </c>
       <c r="C35" s="19" t="n"/>
       <c r="D35" s="10" t="n">
-        <v>4284</v>
+        <v>4712.4</v>
       </c>
       <c r="E35" s="3" t="n"/>
     </row>
@@ -1204,7 +1188,7 @@
       </c>
       <c r="C36" s="19" t="n"/>
       <c r="D36" s="8" t="n">
-        <v>4038</v>
+        <v>4441.8</v>
       </c>
       <c r="E36" s="3" t="n"/>
     </row>
@@ -1221,7 +1205,7 @@
       </c>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="10" t="n">
-        <v>3784</v>
+        <v>4162.4</v>
       </c>
       <c r="E37" s="3" t="n"/>
     </row>
@@ -1238,14 +1222,14 @@
       </c>
       <c r="C38" s="19" t="n"/>
       <c r="D38" s="8" t="n">
-        <v>5983</v>
+        <v>6581.3</v>
       </c>
       <c r="E38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  </t>
+          <t>  </t>
         </is>
       </c>
     </row>
@@ -1256,8 +1240,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -1268,19 +1250,19 @@
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
+++ b/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
@@ -984,7 +984,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
+++ b/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
@@ -984,7 +984,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
+++ b/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
@@ -984,7 +984,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45255</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
+++ b/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
@@ -984,7 +984,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
+++ b/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
@@ -984,7 +984,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
+++ b/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
@@ -984,7 +984,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45267</v>
+        <v>45257.55651770745</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1057,6 +1057,8 @@
       </c>
       <c r="E11" s="20" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
@@ -1064,6 +1066,12 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
@@ -1071,6 +1079,14 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30" ht="18" customHeight="1" s="17">
       <c r="A30" s="12" t="inlineStr">
         <is>
@@ -1103,7 +1119,7 @@
       </c>
       <c r="C31" s="19" t="n"/>
       <c r="D31" s="8" t="n">
-        <v>4359.3</v>
+        <v>6318.19</v>
       </c>
       <c r="E31" s="3" t="n"/>
     </row>
@@ -1120,7 +1136,7 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="10" t="n">
-        <v>3888.5</v>
+        <v>5635.83</v>
       </c>
       <c r="E32" s="3" t="n"/>
     </row>
@@ -1137,7 +1153,7 @@
       </c>
       <c r="C33" s="19" t="n"/>
       <c r="D33" s="8" t="n">
-        <v>3708.1</v>
+        <v>5374.37</v>
       </c>
       <c r="E33" s="3" t="n"/>
     </row>
@@ -1154,7 +1170,7 @@
       </c>
       <c r="C34" s="19" t="n"/>
       <c r="D34" s="10" t="n">
-        <v>6315.1</v>
+        <v>9152.85</v>
       </c>
       <c r="E34" s="3" t="n"/>
     </row>
@@ -1171,7 +1187,7 @@
       </c>
       <c r="C35" s="19" t="n"/>
       <c r="D35" s="10" t="n">
-        <v>4712.4</v>
+        <v>6829.96</v>
       </c>
       <c r="E35" s="3" t="n"/>
     </row>
@@ -1188,7 +1204,7 @@
       </c>
       <c r="C36" s="19" t="n"/>
       <c r="D36" s="8" t="n">
-        <v>4441.8</v>
+        <v>6437.76</v>
       </c>
       <c r="E36" s="3" t="n"/>
     </row>
@@ -1205,7 +1221,7 @@
       </c>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="10" t="n">
-        <v>4162.4</v>
+        <v>6032.81</v>
       </c>
       <c r="E37" s="3" t="n"/>
     </row>
@@ -1222,14 +1238,14 @@
       </c>
       <c r="C38" s="19" t="n"/>
       <c r="D38" s="8" t="n">
-        <v>6581.3</v>
+        <v>9538.67</v>
       </c>
       <c r="E38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="D39" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve">  </t>
         </is>
       </c>
     </row>
@@ -1240,6 +1256,8 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -1250,19 +1268,19 @@
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
+++ b/LISTAS/mi/TARUGO UNIVERSAL DISMAY.xlsx
@@ -984,7 +984,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45257.55651770745</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1057,8 +1057,6 @@
       </c>
       <c r="E11" s="20" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
@@ -1066,12 +1064,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
@@ -1079,14 +1071,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30" ht="18" customHeight="1" s="17">
       <c r="A30" s="12" t="inlineStr">
         <is>
@@ -1119,7 +1103,7 @@
       </c>
       <c r="C31" s="19" t="n"/>
       <c r="D31" s="8" t="n">
-        <v>6318.19</v>
+        <v>4359.3</v>
       </c>
       <c r="E31" s="3" t="n"/>
     </row>
@@ -1136,7 +1120,7 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="10" t="n">
-        <v>5635.83</v>
+        <v>3888.5</v>
       </c>
       <c r="E32" s="3" t="n"/>
     </row>
@@ -1153,7 +1137,7 @@
       </c>
       <c r="C33" s="19" t="n"/>
       <c r="D33" s="8" t="n">
-        <v>5374.37</v>
+        <v>3708.1</v>
       </c>
       <c r="E33" s="3" t="n"/>
     </row>
@@ -1170,7 +1154,7 @@
       </c>
       <c r="C34" s="19" t="n"/>
       <c r="D34" s="10" t="n">
-        <v>9152.85</v>
+        <v>6315.1</v>
       </c>
       <c r="E34" s="3" t="n"/>
     </row>
@@ -1187,7 +1171,7 @@
       </c>
       <c r="C35" s="19" t="n"/>
       <c r="D35" s="10" t="n">
-        <v>6829.96</v>
+        <v>4712.4</v>
       </c>
       <c r="E35" s="3" t="n"/>
     </row>
@@ -1204,7 +1188,7 @@
       </c>
       <c r="C36" s="19" t="n"/>
       <c r="D36" s="8" t="n">
-        <v>6437.76</v>
+        <v>4441.8</v>
       </c>
       <c r="E36" s="3" t="n"/>
     </row>
@@ -1221,7 +1205,7 @@
       </c>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="10" t="n">
-        <v>6032.81</v>
+        <v>4162.4</v>
       </c>
       <c r="E37" s="3" t="n"/>
     </row>
@@ -1238,14 +1222,14 @@
       </c>
       <c r="C38" s="19" t="n"/>
       <c r="D38" s="8" t="n">
-        <v>9538.67</v>
+        <v>6581.3</v>
       </c>
       <c r="E38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  </t>
+          <t>  </t>
         </is>
       </c>
     </row>
@@ -1256,8 +1240,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -1267,20 +1249,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
